--- a/stories/arbres/TREE-SOC-031.xlsx
+++ b/stories/arbres/TREE-SOC-031.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Lila est avec papa, dans la cuisine. Lila a envie de jouer. papa est là, tout près. On va apprendre : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila écoute papa. Lila entend les mots : travail, acheter pain légumes chaussures.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Lila va vers la cuisine. Un vélo passe au loin. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Lila se souvient : travail, acheter pain légumes chaussures. Voici le geste : dire à quoi ça sert. On rit un peu. papa dit : je suis là. On reste ensemble.</t>
+          <t>Lila va vers la cuisine. Un vélo passe au loin. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Lila se souvient : travail, acheter pain légumes chaussures. Voici le geste : dire à quoi ça sert. On rit un peu. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Lila va vers la cuisine. Un vélo passe au loin. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Lila se souvient : travail, acheter pain légumes chaussures. Voici le geste : dire à quoi ça sert. On rit un peu.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1858,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? À quoi sert l'argent.</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2031,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : dire à quoi ça sert. Lila respire. Lila retient : travail, acheter pain légumes chaussures. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2222,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2389,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi les cubes. Il y a des miettes sur la table. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire à quoi ça sert. Lila répète tout bas : travail, acheter pain légumes chaussures. On range un objet. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2580,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2747,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le matin. La couverture est douce. On rit un peu. Cette fin-là est celle de la cuisine, les cubes et le matin. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2914,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3081,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint après la sieste. On entend un oiseau. On se tait une seconde. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3248,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3415,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le soir. Ça sent le pain chaud. On se tient la main. Cette fin-là est celle de la cuisine, les cubes et le soir. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3582,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3749,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le livre. Un chat miaule une fois. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire à quoi ça sert. Lila répète tout bas : travail, acheter pain légumes chaussures. On dit merci. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3940,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4107,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le matin. On entend un oiseau. On rit un peu. Cette fin-là est celle de la cuisine, le livre et le matin. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4274,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4441,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint après la sieste. Ça sent le pain chaud. On se tait une seconde. Cette fin-là est celle de la cuisine, le livre et après la sieste. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4608,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4775,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le soir. Le vent est doux. On se tient la main. Cette fin-là est celle de la cuisine, le livre et le soir. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4942,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5109,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi la dînette. Les chaussures font toc toc. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire à quoi ça sert. Lila répète tout bas : travail, acheter pain légumes chaussures. On souffle doucement. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5300,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5467,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le matin. Ça sent le pain chaud. On rit un peu. Cette fin-là est celle de la cuisine, la dînette et le matin. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5634,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5801,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint après la sieste. Le vent est doux. On se tait une seconde. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5968,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6135,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le soir. Le sol est un peu froid. On se tient la main. Cette fin-là est celle de la cuisine, la dînette et le soir. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6302,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6163,7 +6331,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Lila va vers le jardin. La lumière est claire. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Lila se souvient : travail, acheter pain légumes chaussures. Voici le geste : dire à quoi ça sert. On se tait une seconde. papa dit : je suis là. On reste ensemble.</t>
+          <t>Lila va vers le jardin. La lumière est claire. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Lila se souvient : travail, acheter pain légumes chaussures. Voici le geste : dire à quoi ça sert. On se tait une seconde. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6301,6 +6469,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Lila va vers le jardin. La lumière est claire. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Lila se souvient : travail, acheter pain légumes chaussures. Voici le geste : dire à quoi ça sert. On se tait une seconde.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6477,6 +6651,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? À quoi sert l'argent.</t>
         </is>
       </c>
     </row>
@@ -6645,6 +6824,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : dire à quoi ça sert. Lila respire. Lila retient : travail, acheter pain légumes chaussures. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6831,6 +7015,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6993,6 +7182,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi les cubes. La couverture est douce. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire à quoi ça sert. Lila répète tout bas : travail, acheter pain légumes chaussures. On range un objet. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7179,6 +7373,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7341,6 +7540,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le matin. On entend un oiseau. On se tait une seconde. Cette fin-là est celle de le jardin, les cubes et le matin. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,6 +7707,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7665,6 +7874,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint après la sieste. Ça sent le pain chaud. On se tient la main. Cette fin-là est celle de le jardin, les cubes et après la sieste. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7827,6 +8041,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7989,6 +8208,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le soir. Le vent est doux. On range un objet. Cette fin-là est celle de le jardin, les cubes et le soir. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8151,6 +8375,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8313,6 +8542,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le livre. On entend un oiseau. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire à quoi ça sert. Lila répète tout bas : travail, acheter pain légumes chaussures. On dit merci. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8499,6 +8733,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8661,6 +8900,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le matin. Ça sent le pain chaud. On se tait une seconde. Cette fin-là est celle de le jardin, le livre et le matin. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8823,6 +9067,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8985,6 +9234,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint après la sieste. Le vent est doux. On se tient la main. Cette fin-là est celle de le jardin, le livre et après la sieste. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9147,6 +9401,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9309,6 +9568,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le soir. Le sol est un peu froid. On range un objet. Cette fin-là est celle de le jardin, le livre et le soir. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9471,6 +9735,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9633,6 +9902,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi la dînette. Ça sent le pain chaud. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire à quoi ça sert. Lila répète tout bas : travail, acheter pain légumes chaussures. On souffle doucement. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9819,6 +10093,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9981,6 +10260,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le matin. Le vent est doux. On se tait une seconde. Cette fin-là est celle de le jardin, la dînette et le matin. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10143,6 +10427,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10305,6 +10594,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint après la sieste. Le sol est un peu froid. On se tient la main. Cette fin-là est celle de le jardin, la dînette et après la sieste. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10467,6 +10761,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10629,6 +10928,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le soir. Une feuille tombe. On range un objet. Cette fin-là est celle de le jardin, la dînette et le soir. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10791,6 +11095,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10815,7 +11124,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Lila va vers la chambre. Il y a des miettes sur la table. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Lila se souvient : travail, acheter pain légumes chaussures. Voici le geste : dire à quoi ça sert. On se tient la main. papa dit : je suis là. On reste ensemble.</t>
+          <t>Lila va vers la chambre. Il y a des miettes sur la table. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Lila se souvient : travail, acheter pain légumes chaussures. Voici le geste : dire à quoi ça sert. On se tient la main. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10953,6 +11262,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Lila va vers la chambre. Il y a des miettes sur la table. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Lila se souvient : travail, acheter pain légumes chaussures. Voici le geste : dire à quoi ça sert. On se tient la main.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11129,6 +11444,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? À quoi sert l'argent.</t>
         </is>
       </c>
     </row>
@@ -11297,6 +11617,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : dire à quoi ça sert. Lila respire. Lila retient : travail, acheter pain légumes chaussures. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11483,6 +11808,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11645,6 +11975,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi les cubes. Le vent est doux. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire à quoi ça sert. Lila répète tout bas : travail, acheter pain légumes chaussures. On range un objet. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11831,6 +12166,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11993,6 +12333,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le matin. Ça sent le pain chaud. On se tient la main. Cette fin-là est celle de la chambre, les cubes et le matin. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12155,6 +12500,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12317,6 +12667,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint après la sieste. Le vent est doux. On range un objet. Cette fin-là est celle de la chambre, les cubes et après la sieste. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12479,6 +12834,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12641,6 +13001,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le soir. Le sol est un peu froid. On dit merci. Cette fin-là est celle de la chambre, les cubes et le soir. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12803,6 +13168,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12965,6 +13335,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le livre. Le sol est un peu froid. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire à quoi ça sert. Lila répète tout bas : travail, acheter pain légumes chaussures. On dit merci. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13151,6 +13526,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13313,6 +13693,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le matin. Le vent est doux. On se tient la main. Cette fin-là est celle de la chambre, le livre et le matin. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13475,6 +13860,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13637,6 +14027,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint après la sieste. Le sol est un peu froid. On range un objet. Cette fin-là est celle de la chambre, le livre et après la sieste. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13799,6 +14194,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13961,6 +14361,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le soir. Une feuille tombe. On dit merci. Cette fin-là est celle de la chambre, le livre et le soir. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14123,6 +14528,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14285,6 +14695,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi la dînette. Une feuille tombe. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire à quoi ça sert. Lila répète tout bas : travail, acheter pain légumes chaussures. On souffle doucement. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14471,6 +14886,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14633,6 +15053,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le matin. Le sol est un peu froid. On se tient la main. Cette fin-là est celle de la chambre, la dînette et le matin. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14795,6 +15220,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14957,6 +15387,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint après la sieste. Une feuille tombe. On range un objet. Cette fin-là est celle de la chambre, la dînette et après la sieste. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15119,6 +15554,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15281,6 +15721,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le soir. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de la chambre, la dînette et le soir. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15443,6 +15888,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15461,7 +15911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15478,6 +15928,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SOC-031.xlsx
+++ b/stories/arbres/TREE-SOC-031.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Lila est avec papa, dans la cuisine. Lila a envie de jouer. papa est là, tout près. On va apprendre : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila écoute papa. Lila entend les mots : travail, acheter pain légumes chaussures.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1865,6 +1873,7 @@
           <t>narrateur|Que fait-on ? À quoi sert l'argent.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2036,6 +2045,7 @@
           <t>narrateur|Oui. Voici le geste : dire à quoi ça sert. Lila respire. Lila retient : travail, acheter pain légumes chaussures. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2227,6 +2237,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2394,6 +2405,7 @@
           <t>narrateur|Lila a choisi les cubes. Il y a des miettes sur la table. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire à quoi ça sert. Lila répète tout bas : travail, acheter pain légumes chaussures. On range un objet. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2585,6 +2597,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2752,6 +2765,7 @@
           <t>narrateur|Lila rejoint le matin. La couverture est douce. On rit un peu. Cette fin-là est celle de la cuisine, les cubes et le matin. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2919,6 +2933,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3086,6 +3101,7 @@
           <t>narrateur|Lila rejoint après la sieste. On entend un oiseau. On se tait une seconde. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3253,6 +3269,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3420,6 +3437,7 @@
           <t>narrateur|Lila rejoint le soir. Ça sent le pain chaud. On se tient la main. Cette fin-là est celle de la cuisine, les cubes et le soir. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3587,6 +3605,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3754,6 +3773,7 @@
           <t>narrateur|Lila a choisi le livre. Un chat miaule une fois. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire à quoi ça sert. Lila répète tout bas : travail, acheter pain légumes chaussures. On dit merci. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3945,6 +3965,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4112,6 +4133,7 @@
           <t>narrateur|Lila rejoint le matin. On entend un oiseau. On rit un peu. Cette fin-là est celle de la cuisine, le livre et le matin. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4279,6 +4301,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4446,6 +4469,7 @@
           <t>narrateur|Lila rejoint après la sieste. Ça sent le pain chaud. On se tait une seconde. Cette fin-là est celle de la cuisine, le livre et après la sieste. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4613,6 +4637,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4780,6 +4805,7 @@
           <t>narrateur|Lila rejoint le soir. Le vent est doux. On se tient la main. Cette fin-là est celle de la cuisine, le livre et le soir. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4947,6 +4973,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5114,6 +5141,7 @@
           <t>narrateur|Lila a choisi la dînette. Les chaussures font toc toc. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire à quoi ça sert. Lila répète tout bas : travail, acheter pain légumes chaussures. On souffle doucement. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5305,6 +5333,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5472,6 +5501,7 @@
           <t>narrateur|Lila rejoint le matin. Ça sent le pain chaud. On rit un peu. Cette fin-là est celle de la cuisine, la dînette et le matin. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5639,6 +5669,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5806,6 +5837,7 @@
           <t>narrateur|Lila rejoint après la sieste. Le vent est doux. On se tait une seconde. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5973,6 +6005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6140,6 +6173,7 @@
           <t>narrateur|Lila rejoint le soir. Le sol est un peu froid. On se tient la main. Cette fin-là est celle de la cuisine, la dînette et le soir. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6307,6 +6341,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6475,6 +6510,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6658,6 +6694,7 @@
           <t>narrateur|Que fait-on ? À quoi sert l'argent.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6829,6 +6866,7 @@
           <t>narrateur|Oui. Voici le geste : dire à quoi ça sert. Lila respire. Lila retient : travail, acheter pain légumes chaussures. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7020,6 +7058,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7187,6 +7226,7 @@
           <t>narrateur|Lila a choisi les cubes. La couverture est douce. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire à quoi ça sert. Lila répète tout bas : travail, acheter pain légumes chaussures. On range un objet. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7378,6 +7418,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7545,6 +7586,7 @@
           <t>narrateur|Lila rejoint le matin. On entend un oiseau. On se tait une seconde. Cette fin-là est celle de le jardin, les cubes et le matin. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7712,6 +7754,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7879,6 +7922,7 @@
           <t>narrateur|Lila rejoint après la sieste. Ça sent le pain chaud. On se tient la main. Cette fin-là est celle de le jardin, les cubes et après la sieste. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8046,6 +8090,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8213,6 +8258,7 @@
           <t>narrateur|Lila rejoint le soir. Le vent est doux. On range un objet. Cette fin-là est celle de le jardin, les cubes et le soir. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8380,6 +8426,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8547,6 +8594,7 @@
           <t>narrateur|Lila a choisi le livre. On entend un oiseau. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire à quoi ça sert. Lila répète tout bas : travail, acheter pain légumes chaussures. On dit merci. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8738,6 +8786,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8905,6 +8954,7 @@
           <t>narrateur|Lila rejoint le matin. Ça sent le pain chaud. On se tait une seconde. Cette fin-là est celle de le jardin, le livre et le matin. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9072,6 +9122,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9239,6 +9290,7 @@
           <t>narrateur|Lila rejoint après la sieste. Le vent est doux. On se tient la main. Cette fin-là est celle de le jardin, le livre et après la sieste. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9406,6 +9458,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9573,6 +9626,7 @@
           <t>narrateur|Lila rejoint le soir. Le sol est un peu froid. On range un objet. Cette fin-là est celle de le jardin, le livre et le soir. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9740,6 +9794,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9907,6 +9962,7 @@
           <t>narrateur|Lila a choisi la dînette. Ça sent le pain chaud. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire à quoi ça sert. Lila répète tout bas : travail, acheter pain légumes chaussures. On souffle doucement. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10098,6 +10154,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10265,6 +10322,7 @@
           <t>narrateur|Lila rejoint le matin. Le vent est doux. On se tait une seconde. Cette fin-là est celle de le jardin, la dînette et le matin. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10432,6 +10490,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10599,6 +10658,7 @@
           <t>narrateur|Lila rejoint après la sieste. Le sol est un peu froid. On se tient la main. Cette fin-là est celle de le jardin, la dînette et après la sieste. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10766,6 +10826,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10933,6 +10994,7 @@
           <t>narrateur|Lila rejoint le soir. Une feuille tombe. On range un objet. Cette fin-là est celle de le jardin, la dînette et le soir. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11100,6 +11162,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11268,6 +11331,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11451,6 +11515,7 @@
           <t>narrateur|Que fait-on ? À quoi sert l'argent.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11622,6 +11687,7 @@
           <t>narrateur|Oui. Voici le geste : dire à quoi ça sert. Lila respire. Lila retient : travail, acheter pain légumes chaussures. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11813,6 +11879,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11980,6 +12047,7 @@
           <t>narrateur|Lila a choisi les cubes. Le vent est doux. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire à quoi ça sert. Lila répète tout bas : travail, acheter pain légumes chaussures. On range un objet. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12171,6 +12239,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12338,6 +12407,7 @@
           <t>narrateur|Lila rejoint le matin. Ça sent le pain chaud. On se tient la main. Cette fin-là est celle de la chambre, les cubes et le matin. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12505,6 +12575,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12672,6 +12743,7 @@
           <t>narrateur|Lila rejoint après la sieste. Le vent est doux. On range un objet. Cette fin-là est celle de la chambre, les cubes et après la sieste. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12839,6 +12911,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13006,6 +13079,7 @@
           <t>narrateur|Lila rejoint le soir. Le sol est un peu froid. On dit merci. Cette fin-là est celle de la chambre, les cubes et le soir. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13173,6 +13247,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13340,6 +13415,7 @@
           <t>narrateur|Lila a choisi le livre. Le sol est un peu froid. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire à quoi ça sert. Lila répète tout bas : travail, acheter pain légumes chaussures. On dit merci. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13531,6 +13607,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13698,6 +13775,7 @@
           <t>narrateur|Lila rejoint le matin. Le vent est doux. On se tient la main. Cette fin-là est celle de la chambre, le livre et le matin. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13865,6 +13943,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14032,6 +14111,7 @@
           <t>narrateur|Lila rejoint après la sieste. Le sol est un peu froid. On range un objet. Cette fin-là est celle de la chambre, le livre et après la sieste. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14199,6 +14279,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14366,6 +14447,7 @@
           <t>narrateur|Lila rejoint le soir. Une feuille tombe. On dit merci. Cette fin-là est celle de la chambre, le livre et le soir. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14533,6 +14615,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14700,6 +14783,7 @@
           <t>narrateur|Lila a choisi la dînette. Une feuille tombe. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire à quoi ça sert. Lila répète tout bas : travail, acheter pain légumes chaussures. On souffle doucement. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14891,6 +14975,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15058,6 +15143,7 @@
           <t>narrateur|Lila rejoint le matin. Le sol est un peu froid. On se tient la main. Cette fin-là est celle de la chambre, la dînette et le matin. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15225,6 +15311,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15392,6 +15479,7 @@
           <t>narrateur|Lila rejoint après la sieste. Une feuille tombe. On range un objet. Cette fin-là est celle de la chambre, la dînette et après la sieste. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15559,6 +15647,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15726,6 +15815,7 @@
           <t>narrateur|Lila rejoint le soir. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de la chambre, la dînette et le soir. Lila a appris : À quoi sert l'argent. Voici le geste : dire à quoi ça sert. Lila a entendu : travail, acheter pain légumes chaussures. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15893,6 +15983,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15911,7 +16002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15935,6 +16026,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15949,7 +16054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16136,6 +16241,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
